--- a/assets/template.xlsx
+++ b/assets/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Work\maintenance\BA MANUAL MATERIAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Work\my-telegram-bot\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37745398-DBB0-4E5D-8825-A6AFFC509211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E58D351-7D3A-4FFD-BFAD-74ED64EBFD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BA" sheetId="356" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="60">
   <si>
     <t xml:space="preserve">Nomor *)                                                     </t>
   </si>
@@ -191,6 +191,27 @@
   </si>
   <si>
     <t>CIREBON</t>
+  </si>
+  <si>
+    <t>BERITA ACARA PENGELUARAN BARANG (BAPB)</t>
+  </si>
+  <si>
+    <t>REVISI : 01</t>
+  </si>
+  <si>
+    <t>HALAMAN : 1/1</t>
+  </si>
+  <si>
+    <t>QHS - TELKOM AKSES</t>
+  </si>
+  <si>
+    <t>TGL.TERBIT : 07/03/2017</t>
+  </si>
+  <si>
+    <t>TA.FR-025-04</t>
+  </si>
+  <si>
+    <t>FORM</t>
   </si>
 </sst>
 </file>
@@ -202,7 +223,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -289,8 +310,28 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -309,6 +350,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -499,7 +546,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
@@ -590,9 +637,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -632,15 +694,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>230395</xdr:colOff>
+      <xdr:colOff>154195</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>68580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2234355</xdr:colOff>
+      <xdr:colOff>2158155</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>113634</xdr:rowOff>
+      <xdr:rowOff>182214</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -663,52 +725,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6052820" y="0"/>
-          <a:ext cx="2004060" cy="665480"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>50809</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>185738</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="28575" y="774709"/>
-          <a:ext cx="8186738" cy="1430329"/>
+          <a:off x="5541535" y="68580"/>
+          <a:ext cx="2003960" cy="662274"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -721,13 +739,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>835138</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>20409</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -742,7 +760,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1100,7 +1118,7 @@
   <sheetPr>
     <tabColor indexed="49"/>
   </sheetPr>
-  <dimension ref="A6:L53"/>
+  <dimension ref="A5:L52"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.5546875" style="1" customWidth="1"/>
@@ -1116,30 +1134,92 @@
     <col min="11" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="1:12">
-      <c r="G6" s="2"/>
+    <row r="5" spans="1:12" ht="7.8" customHeight="1">
+      <c r="A5" s="33"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+    </row>
+    <row r="6" spans="1:12" ht="21">
+      <c r="A6" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="21">
-      <c r="A10" s="33"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
+    <row r="7" spans="1:12" ht="18">
+      <c r="A7" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="36"/>
+      <c r="C7" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="37" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="18">
+      <c r="A8" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="36"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="21">
+      <c r="A9" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+    </row>
+    <row r="10" spans="1:12" ht="16.8">
+      <c r="A10" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="23"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
     </row>
     <row r="11" spans="1:12" ht="16.8">
       <c r="A11" s="24" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" s="24"/>
       <c r="C11" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>43</v>
-      </c>
+      <c r="D11" s="4"/>
       <c r="H11" s="23"/>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
@@ -1148,13 +1228,13 @@
     </row>
     <row r="12" spans="1:12" ht="16.8">
       <c r="A12" s="24" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" s="24"/>
       <c r="C12" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="5"/>
       <c r="H12" s="23"/>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
@@ -1163,13 +1243,13 @@
     </row>
     <row r="13" spans="1:12" ht="16.8">
       <c r="A13" s="24" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" s="24"/>
       <c r="C13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="5"/>
+      <c r="D13" s="4"/>
       <c r="H13" s="23"/>
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
@@ -1177,33 +1257,36 @@
       <c r="L13" s="15"/>
     </row>
     <row r="14" spans="1:12" ht="16.8">
-      <c r="A14" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="24"/>
+      <c r="A14" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="13"/>
       <c r="C14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
       <c r="H14" s="23"/>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
     </row>
-    <row r="15" spans="1:12" ht="16.8">
-      <c r="A15" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="13"/>
+    <row r="15" spans="1:12" ht="15.6">
+      <c r="A15" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="24"/>
       <c r="C15" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="23"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="15"/>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
@@ -1211,7 +1294,7 @@
     </row>
     <row r="16" spans="1:12" ht="15.6">
       <c r="A16" s="24" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="3" t="s">
@@ -1221,66 +1304,59 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.6">
-      <c r="A17" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="3" t="s">
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" ht="18">
+      <c r="A18" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="26"/>
+      <c r="G18" s="27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18">
+      <c r="A19" s="30"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="28"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.6">
+      <c r="A20" s="17">
         <v>1</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" ht="18">
-      <c r="A19" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="26"/>
-      <c r="G19" s="27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="18">
-      <c r="A20" s="30"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="28"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
     </row>
     <row r="21" spans="1:7" ht="15.6">
       <c r="A21" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -1291,7 +1367,7 @@
     </row>
     <row r="22" spans="1:7" ht="15.6">
       <c r="A22" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -1302,7 +1378,7 @@
     </row>
     <row r="23" spans="1:7" ht="15.6">
       <c r="A23" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -1313,7 +1389,7 @@
     </row>
     <row r="24" spans="1:7" ht="15.6">
       <c r="A24" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -1324,7 +1400,7 @@
     </row>
     <row r="25" spans="1:7" ht="15.6">
       <c r="A25" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -1335,7 +1411,7 @@
     </row>
     <row r="26" spans="1:7" ht="15.6">
       <c r="A26" s="17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -1346,7 +1422,7 @@
     </row>
     <row r="27" spans="1:7" ht="15.6">
       <c r="A27" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -1355,9 +1431,9 @@
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
     </row>
-    <row r="28" spans="1:7" ht="15.6">
+    <row r="28" spans="1:7" ht="18.600000000000001" customHeight="1">
       <c r="A28" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -1368,7 +1444,7 @@
     </row>
     <row r="29" spans="1:7" ht="18.600000000000001" customHeight="1">
       <c r="A29" s="17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -1377,9 +1453,9 @@
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
     </row>
-    <row r="30" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="30" spans="1:7" ht="15.6">
       <c r="A30" s="17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -1390,7 +1466,7 @@
     </row>
     <row r="31" spans="1:7" ht="15.6">
       <c r="A31" s="17">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -1400,28 +1476,30 @@
       <c r="G31" s="17"/>
     </row>
     <row r="32" spans="1:7" ht="15.6">
-      <c r="A32" s="17">
-        <v>12</v>
-      </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
     </row>
     <row r="33" spans="1:8" ht="15.6">
-      <c r="A33" s="3"/>
+      <c r="A33" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
+      <c r="G33" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="34" spans="1:8" ht="15.6">
       <c r="A34" s="4" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1429,21 +1507,18 @@
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4" t="s">
-        <v>15</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" ht="15.6">
-      <c r="A35" s="4" t="s">
-        <v>48</v>
-      </c>
+      <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
-      <c r="G35" s="4" t="s">
-        <v>44</v>
-      </c>
+      <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" ht="15.6">
@@ -1477,79 +1552,80 @@
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" ht="15.6">
-      <c r="A39" s="4"/>
+      <c r="A39" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
+      <c r="G39" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" ht="15.6">
-      <c r="A40" s="11" t="s">
-        <v>46</v>
+      <c r="A40" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
-      <c r="G40" s="11" t="s">
-        <v>36</v>
+      <c r="G40" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" ht="15.6">
-      <c r="A41" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="A41" s="7"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
-      <c r="G41" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H41" s="4"/>
+      <c r="G41" s="7"/>
     </row>
     <row r="42" spans="1:8" ht="15.6">
-      <c r="A42" s="7"/>
+      <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
-      <c r="G42" s="7"/>
+      <c r="G42" s="4"/>
     </row>
     <row r="43" spans="1:8" ht="15.6">
-      <c r="A43" s="4"/>
+      <c r="A43" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
+      <c r="G43" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="44" spans="1:8" ht="15.6">
-      <c r="A44" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
-      <c r="G44" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="G44" s="4"/>
     </row>
     <row r="45" spans="1:8" ht="15.6">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
+      <c r="D45" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
@@ -1559,7 +1635,7 @@
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -1569,9 +1645,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
-      <c r="D47" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
@@ -1586,68 +1660,63 @@
       <c r="G48" s="4"/>
     </row>
     <row r="49" spans="1:10" ht="15.6">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
+      <c r="A49" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="11"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
+      <c r="G49" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J49" s="12"/>
     </row>
     <row r="50" spans="1:10" ht="15.6">
-      <c r="A50" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B50" s="11"/>
+      <c r="A50" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" s="7"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
-      <c r="G50" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J50" s="12"/>
+      <c r="G50" s="7" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="51" spans="1:10" ht="15.6">
-      <c r="A51" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
+      <c r="D51" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="7" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="52" spans="1:10" ht="15.6">
-      <c r="D52" s="11" t="s">
-        <v>19</v>
+      <c r="D52" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="E52" s="4"/>
     </row>
-    <row r="53" spans="1:10" ht="15.6">
-      <c r="D53" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E53" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A10:G10"/>
+  <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="C7:F8"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/assets/template.xlsx
+++ b/assets/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Work\my-telegram-bot\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E58D351-7D3A-4FFD-BFAD-74ED64EBFD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7B27A2-52E6-43CD-B44A-D0B5EFAF6457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -546,7 +546,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
@@ -609,6 +609,33 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -634,27 +661,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -739,13 +745,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>835138</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>20409</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1118,7 +1124,7 @@
   <sheetPr>
     <tabColor indexed="49"/>
   </sheetPr>
-  <dimension ref="A5:L52"/>
+  <dimension ref="A5:L53"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.5546875" style="1" customWidth="1"/>
@@ -1135,91 +1141,85 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:12" ht="7.8" customHeight="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="21">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:12" ht="18">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="35" t="s">
+      <c r="B7" s="29"/>
+      <c r="C7" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="37" t="s">
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="26" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="18">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="37" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="26" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="21">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-    </row>
-    <row r="10" spans="1:12" ht="16.8">
-      <c r="A10" s="24" t="s">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+    </row>
+    <row r="10" spans="1:12" ht="21" hidden="1">
+      <c r="A10" s="27"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.8">
+      <c r="A11" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="23"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-    </row>
-    <row r="11" spans="1:12" ht="16.8">
-      <c r="A11" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="24"/>
+      <c r="B11" s="33"/>
       <c r="C11" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="H11" s="23"/>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
@@ -1227,14 +1227,14 @@
       <c r="L11" s="15"/>
     </row>
     <row r="12" spans="1:12" ht="16.8">
-      <c r="A12" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="24"/>
+      <c r="A12" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="33"/>
       <c r="C12" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="5"/>
+      <c r="D12" s="4"/>
       <c r="H12" s="23"/>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
@@ -1242,14 +1242,14 @@
       <c r="L12" s="15"/>
     </row>
     <row r="13" spans="1:12" ht="16.8">
-      <c r="A13" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="24"/>
+      <c r="A13" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="33"/>
       <c r="C13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="5"/>
       <c r="H13" s="23"/>
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
@@ -1257,46 +1257,43 @@
       <c r="L13" s="15"/>
     </row>
     <row r="14" spans="1:12" ht="16.8">
-      <c r="A14" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="13"/>
+      <c r="A14" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="33"/>
       <c r="C14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
+      <c r="D14" s="4"/>
       <c r="H14" s="23"/>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
     </row>
-    <row r="15" spans="1:12" ht="15.6">
-      <c r="A15" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="24"/>
+    <row r="15" spans="1:12" ht="16.8">
+      <c r="A15" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="13"/>
       <c r="C15" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="15"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="23"/>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
       <c r="L15" s="15"/>
     </row>
     <row r="16" spans="1:12" ht="15.6">
-      <c r="A16" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="24"/>
+      <c r="A16" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="33"/>
       <c r="C16" s="3" t="s">
         <v>1</v>
       </c>
@@ -1304,59 +1301,66 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
-    </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" ht="18">
-      <c r="A18" s="29" t="s">
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.6">
+      <c r="A17" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="33"/>
+      <c r="C17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" ht="18">
+      <c r="A19" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B19" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31" t="s">
+      <c r="C19" s="40"/>
+      <c r="D19" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="E19" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="26"/>
-      <c r="G18" s="27" t="s">
+      <c r="F19" s="35"/>
+      <c r="G19" s="36" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="18">
-      <c r="A19" s="30"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="10" t="s">
+    <row r="20" spans="1:7" ht="18">
+      <c r="A20" s="39"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F20" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="28"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.6">
-      <c r="A20" s="17">
-        <v>1</v>
-      </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
+      <c r="G20" s="37"/>
     </row>
     <row r="21" spans="1:7" ht="15.6">
       <c r="A21" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -1367,7 +1371,7 @@
     </row>
     <row r="22" spans="1:7" ht="15.6">
       <c r="A22" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -1378,7 +1382,7 @@
     </row>
     <row r="23" spans="1:7" ht="15.6">
       <c r="A23" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -1389,7 +1393,7 @@
     </row>
     <row r="24" spans="1:7" ht="15.6">
       <c r="A24" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -1400,7 +1404,7 @@
     </row>
     <row r="25" spans="1:7" ht="15.6">
       <c r="A25" s="17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -1411,7 +1415,7 @@
     </row>
     <row r="26" spans="1:7" ht="15.6">
       <c r="A26" s="17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -1422,7 +1426,7 @@
     </row>
     <row r="27" spans="1:7" ht="15.6">
       <c r="A27" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -1431,9 +1435,9 @@
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
     </row>
-    <row r="28" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="28" spans="1:7" ht="15.6">
       <c r="A28" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -1444,7 +1448,7 @@
     </row>
     <row r="29" spans="1:7" ht="18.600000000000001" customHeight="1">
       <c r="A29" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -1453,9 +1457,9 @@
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
     </row>
-    <row r="30" spans="1:7" ht="15.6">
+    <row r="30" spans="1:7" ht="18.600000000000001" customHeight="1">
       <c r="A30" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -1466,7 +1470,7 @@
     </row>
     <row r="31" spans="1:7" ht="15.6">
       <c r="A31" s="17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -1476,30 +1480,28 @@
       <c r="G31" s="17"/>
     </row>
     <row r="32" spans="1:7" ht="15.6">
-      <c r="A32" s="3"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
+      <c r="A32" s="17">
+        <v>12</v>
+      </c>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
     </row>
     <row r="33" spans="1:8" ht="15.6">
-      <c r="A33" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="A33" s="3"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
-      <c r="G33" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="G33" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="15.6">
       <c r="A34" s="4" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1507,18 +1509,21 @@
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H34" s="4"/>
+        <v>15</v>
+      </c>
     </row>
     <row r="35" spans="1:8" ht="15.6">
-      <c r="A35" s="4"/>
+      <c r="A35" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
+      <c r="G35" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" ht="15.6">
@@ -1552,80 +1557,79 @@
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" ht="15.6">
-      <c r="A39" s="11" t="s">
-        <v>46</v>
-      </c>
+      <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
-      <c r="G39" s="11" t="s">
-        <v>36</v>
-      </c>
+      <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" ht="15.6">
-      <c r="A40" s="7" t="s">
-        <v>47</v>
+      <c r="A40" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
-      <c r="G40" s="7" t="s">
-        <v>45</v>
+      <c r="G40" s="11" t="s">
+        <v>36</v>
       </c>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" ht="15.6">
-      <c r="A41" s="7"/>
+      <c r="A41" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
-      <c r="G41" s="7"/>
+      <c r="G41" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" ht="15.6">
-      <c r="A42" s="4"/>
+      <c r="A42" s="7"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
+      <c r="G42" s="7"/>
     </row>
     <row r="43" spans="1:8" ht="15.6">
-      <c r="A43" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
-      <c r="G43" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="G43" s="4"/>
     </row>
     <row r="44" spans="1:8" ht="15.6">
-      <c r="A44" s="4"/>
+      <c r="A44" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
+      <c r="G44" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="45" spans="1:8" ht="15.6">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
@@ -1635,7 +1639,7 @@
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -1645,7 +1649,9 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
+      <c r="D47" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
@@ -1660,63 +1666,72 @@
       <c r="G48" s="4"/>
     </row>
     <row r="49" spans="1:10" ht="15.6">
-      <c r="A49" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B49" s="11"/>
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
-      <c r="G49" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J49" s="12"/>
+      <c r="G49" s="4"/>
     </row>
     <row r="50" spans="1:10" ht="15.6">
-      <c r="A50" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" s="7"/>
+      <c r="A50" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="11"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
-      <c r="G50" s="7" t="s">
+      <c r="G50" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J50" s="12"/>
+    </row>
+    <row r="51" spans="1:10" ht="15.6">
+      <c r="A51" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15.6">
-      <c r="D51" s="11" t="s">
+    <row r="52" spans="1:10" ht="15.6">
+      <c r="D52" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E51" s="4"/>
-    </row>
-    <row r="52" spans="1:10" ht="15.6">
-      <c r="D52" s="7" t="s">
+      <c r="E52" s="4"/>
+    </row>
+    <row r="53" spans="1:10" ht="15.6">
+      <c r="D53" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E52" s="4"/>
+      <c r="E53" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="C7:F8"/>
-    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
